--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>49.1687</v>
+        <v>50.0479</v>
       </c>
       <c r="E2" t="n">
-        <v>40.6424</v>
+        <v>41.8679</v>
       </c>
       <c r="F2" t="n">
-        <v>8.525700000000001</v>
+        <v>8.180099999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>48.7151</v>
+        <v>52.7985</v>
       </c>
       <c r="H2" t="n">
-        <v>18.0228</v>
+        <v>16.9084</v>
       </c>
       <c r="I2" t="n">
-        <v>30.6925</v>
+        <v>35.8901</v>
       </c>
       <c r="J2" t="n">
-        <v>67.3642</v>
+        <v>74.4055</v>
       </c>
       <c r="K2" t="n">
-        <v>27.8841</v>
+        <v>26.6362</v>
       </c>
       <c r="L2" t="n">
-        <v>39.4803</v>
+        <v>47.7694</v>
       </c>
       <c r="M2" t="n">
-        <v>-18.6491</v>
+        <v>-21.6069</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.8607</v>
+        <v>-9.7278</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.7883</v>
+        <v>-11.8789</v>
       </c>
       <c r="P2" t="n">
-        <v>-6.5779</v>
+        <v>-4.7801</v>
       </c>
       <c r="Q2" t="n">
-        <v>-59.8839</v>
+        <v>-66.9235</v>
       </c>
       <c r="R2" t="n">
-        <v>53.306</v>
+        <v>62.1435</v>
       </c>
       <c r="S2" t="n">
-        <v>-29.888</v>
+        <v>-37.4956</v>
       </c>
       <c r="T2" t="n">
-        <v>-15.5904</v>
+        <v>-19.0278</v>
       </c>
       <c r="U2" t="n">
-        <v>-14.2976</v>
+        <v>-18.4676</v>
       </c>
       <c r="V2" t="n">
-        <v>36.9195</v>
+        <v>39.5252</v>
       </c>
       <c r="W2" t="n">
-        <v>48.7527</v>
+        <v>53.4135</v>
       </c>
       <c r="X2" t="n">
-        <v>-11.8331</v>
+        <v>-13.8886</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>37.9441</v>
+        <v>37.786</v>
       </c>
       <c r="E3" t="n">
-        <v>23.2209</v>
+        <v>22.3714</v>
       </c>
       <c r="F3" t="n">
-        <v>14.7228</v>
+        <v>15.4144</v>
       </c>
       <c r="G3" t="n">
-        <v>9.035200000000001</v>
+        <v>8.8325</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9683</v>
+        <v>5.581500000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0667</v>
+        <v>3.2514</v>
       </c>
       <c r="J3" t="n">
-        <v>22.2537</v>
+        <v>21.5417</v>
       </c>
       <c r="K3" t="n">
-        <v>11.0668</v>
+        <v>10.3937</v>
       </c>
       <c r="L3" t="n">
-        <v>11.187</v>
+        <v>11.148</v>
       </c>
       <c r="M3" t="n">
-        <v>-13.2183</v>
+        <v>-12.7089</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.0981</v>
+        <v>-4.8118</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.120200000000001</v>
+        <v>-7.896800000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.1756</v>
+        <v>-3.186799999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-33.1178</v>
+        <v>-33.2344</v>
       </c>
       <c r="R3" t="n">
-        <v>29.9419</v>
+        <v>30.0475</v>
       </c>
       <c r="S3" t="n">
-        <v>28.4586</v>
+        <v>28.5526</v>
       </c>
       <c r="T3" t="n">
-        <v>13.6768</v>
+        <v>13.778</v>
       </c>
       <c r="U3" t="n">
-        <v>14.7818</v>
+        <v>14.7748</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6253</v>
+        <v>3.5873</v>
       </c>
       <c r="W3" t="n">
-        <v>20.4082</v>
+        <v>20.2863</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.7826</v>
+        <v>-16.6988</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>21.8506</v>
+        <v>32.3776</v>
       </c>
       <c r="E4" t="n">
-        <v>21.155</v>
+        <v>19.1618</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6955000000000002</v>
+        <v>13.2158</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1076000000000012</v>
+        <v>22.584</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4849</v>
+        <v>13.5498</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.377299999999999</v>
+        <v>9.0341</v>
       </c>
       <c r="J4" t="n">
-        <v>12.1943</v>
+        <v>28.201</v>
       </c>
       <c r="K4" t="n">
-        <v>8.767199999999999</v>
+        <v>15.4661</v>
       </c>
       <c r="L4" t="n">
-        <v>3.4271</v>
+        <v>12.7349</v>
       </c>
       <c r="M4" t="n">
-        <v>-12.0867</v>
+        <v>-5.6172</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.2825</v>
+        <v>-1.9161</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.8043</v>
+        <v>-3.7012</v>
       </c>
       <c r="P4" t="n">
-        <v>14.9707</v>
+        <v>-0.6824999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-9.073399999999999</v>
+        <v>-34.6</v>
       </c>
       <c r="R4" t="n">
-        <v>24.0442</v>
+        <v>33.9174</v>
       </c>
       <c r="S4" t="n">
-        <v>15.1278</v>
+        <v>25.744</v>
       </c>
       <c r="T4" t="n">
-        <v>11.8953</v>
+        <v>20.4708</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2327</v>
+        <v>5.273400000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-8.3559</v>
+        <v>-15.2674</v>
       </c>
       <c r="W4" t="n">
-        <v>6.138500000000001</v>
+        <v>5.0902</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.4943</v>
+        <v>-20.3579</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>19.9891</v>
+        <v>29.7093</v>
       </c>
       <c r="E5" t="n">
-        <v>9.602600000000001</v>
+        <v>25.7585</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3862</v>
+        <v>3.9507</v>
       </c>
       <c r="G5" t="n">
-        <v>18.8355</v>
+        <v>11.0176</v>
       </c>
       <c r="H5" t="n">
-        <v>11.9918</v>
+        <v>12.7958</v>
       </c>
       <c r="I5" t="n">
-        <v>6.843900000000001</v>
+        <v>-1.7786</v>
       </c>
       <c r="J5" t="n">
-        <v>23.3798</v>
+        <v>23.8438</v>
       </c>
       <c r="K5" t="n">
-        <v>13.6775</v>
+        <v>18.5014</v>
       </c>
       <c r="L5" t="n">
-        <v>9.702499999999999</v>
+        <v>5.342000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.5443</v>
+        <v>-12.8257</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6859</v>
+        <v>-5.7054</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.8583</v>
+        <v>-7.120200000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.4023</v>
+        <v>12.2919</v>
       </c>
       <c r="Q5" t="n">
-        <v>-31.9836</v>
+        <v>-18.2108</v>
       </c>
       <c r="R5" t="n">
-        <v>28.5811</v>
+        <v>30.5028</v>
       </c>
       <c r="S5" t="n">
-        <v>20.8178</v>
+        <v>16.7495</v>
       </c>
       <c r="T5" t="n">
-        <v>16.4382</v>
+        <v>13.0852</v>
       </c>
       <c r="U5" t="n">
-        <v>4.3797</v>
+        <v>3.6641</v>
       </c>
       <c r="V5" t="n">
-        <v>-16.2619</v>
+        <v>-10.3501</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7679</v>
+        <v>7.040299999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.0299</v>
+        <v>-17.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>16.2249</v>
+        <v>24.4086</v>
       </c>
       <c r="E6" t="n">
-        <v>5.173</v>
+        <v>7.5528</v>
       </c>
       <c r="F6" t="n">
-        <v>11.0522</v>
+        <v>16.8558</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.911199999999999</v>
+        <v>6.669300000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6071</v>
+        <v>10.6276</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.5183</v>
+        <v>-3.9582</v>
       </c>
       <c r="J6" t="n">
-        <v>9.788899999999998</v>
+        <v>26.2416</v>
       </c>
       <c r="K6" t="n">
-        <v>10.3956</v>
+        <v>17.9314</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6069000000000013</v>
+        <v>8.31</v>
       </c>
       <c r="M6" t="n">
-        <v>-15.7002</v>
+        <v>-19.5722</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.7887</v>
+        <v>-7.3037</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.9116</v>
+        <v>-12.2685</v>
       </c>
       <c r="P6" t="n">
-        <v>17.6932</v>
+        <v>-28.9092</v>
       </c>
       <c r="Q6" t="n">
-        <v>-24.725</v>
+        <v>-82.858</v>
       </c>
       <c r="R6" t="n">
-        <v>42.4181</v>
+        <v>53.9488</v>
       </c>
       <c r="S6" t="n">
-        <v>17.1442</v>
+        <v>-6.4764</v>
       </c>
       <c r="T6" t="n">
-        <v>11.5601</v>
+        <v>-11.4664</v>
       </c>
       <c r="U6" t="n">
-        <v>5.5844</v>
+        <v>4.99</v>
       </c>
       <c r="V6" t="n">
-        <v>-12.7011</v>
+        <v>53.1246</v>
       </c>
       <c r="W6" t="n">
-        <v>8.5489</v>
+        <v>75.6348</v>
       </c>
       <c r="X6" t="n">
-        <v>-21.2499</v>
+        <v>-22.5107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>11.8287</v>
+        <v>15.7511</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7187999999999999</v>
+        <v>2.531000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>11.1102</v>
+        <v>13.2196</v>
       </c>
       <c r="G7" t="n">
-        <v>26.6049</v>
+        <v>-7.782</v>
       </c>
       <c r="H7" t="n">
-        <v>16.5885</v>
+        <v>9.505599999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10.0165</v>
+        <v>-17.2872</v>
       </c>
       <c r="J7" t="n">
-        <v>31.2086</v>
+        <v>12.3549</v>
       </c>
       <c r="K7" t="n">
-        <v>16.5354</v>
+        <v>17.8345</v>
       </c>
       <c r="L7" t="n">
-        <v>14.6735</v>
+        <v>-5.4795</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.6041</v>
+        <v>-20.1368</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05330000000000001</v>
+        <v>-8.3291</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.6576</v>
+        <v>-11.8077</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9071999999999996</v>
+        <v>18.8938</v>
       </c>
       <c r="Q7" t="n">
-        <v>-33.3445</v>
+        <v>-30.7306</v>
       </c>
       <c r="R7" t="n">
-        <v>32.4373</v>
+        <v>49.6243</v>
       </c>
       <c r="S7" t="n">
-        <v>-23.6701</v>
+        <v>18.9297</v>
       </c>
       <c r="T7" t="n">
-        <v>-16.5886</v>
+        <v>11.0002</v>
       </c>
       <c r="U7" t="n">
-        <v>-7.0814</v>
+        <v>7.930000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>9.8017</v>
+        <v>-14.2909</v>
       </c>
       <c r="W7" t="n">
-        <v>19.4433</v>
+        <v>9.9064</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.641500000000001</v>
+        <v>-24.1972</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>1.175399999999998</v>
+        <v>14.4056</v>
       </c>
       <c r="E8" t="n">
-        <v>-11.7795</v>
+        <v>-1.068400000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>12.955</v>
+        <v>15.4738</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.642500000000001</v>
+        <v>34.0069</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3653</v>
+        <v>16.6385</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.0077</v>
+        <v>17.3685</v>
       </c>
       <c r="J8" t="n">
-        <v>12.8422</v>
+        <v>38.9401</v>
       </c>
       <c r="K8" t="n">
-        <v>12.3838</v>
+        <v>15.9156</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4584000000000001</v>
+        <v>23.024</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.4848</v>
+        <v>-4.9331</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.0185</v>
+        <v>0.7227</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.466099999999999</v>
+        <v>-5.6555</v>
       </c>
       <c r="P8" t="n">
-        <v>-27.4468</v>
+        <v>-3.641899999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-73.49419999999999</v>
+        <v>-41.4291</v>
       </c>
       <c r="R8" t="n">
-        <v>46.0472</v>
+        <v>37.7872</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.707599999999999</v>
+        <v>-26.9965</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.49</v>
+        <v>-19.7522</v>
       </c>
       <c r="U8" t="n">
-        <v>4.7827</v>
+        <v>-7.2443</v>
       </c>
       <c r="V8" t="n">
-        <v>34.9725</v>
+        <v>11.0377</v>
       </c>
       <c r="W8" t="n">
-        <v>58.3626</v>
+        <v>21.1734</v>
       </c>
       <c r="X8" t="n">
-        <v>-23.39</v>
+        <v>-10.1358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. RUIZ</t>
+          <t>A. TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,67 +1108,67 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0459</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9354</v>
+        <v>-0.06670000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8895</v>
+        <v>0.7497</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1635</v>
+        <v>0.5111</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4011</v>
+        <v>0.0373</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7623</v>
+        <v>0.4738</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8144</v>
+        <v>0.0517</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6998</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1147</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.349</v>
+        <v>0.4594</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2986</v>
+        <v>-0.01449999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6477000000000001</v>
+        <v>0.4738</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0166</v>
+        <v>-0.007000000000000003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1043</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. MAURI</t>
+          <t>H. RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,61 +1186,61 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2278</v>
+        <v>-0.0429</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6196</v>
+        <v>-0.9437</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6082</v>
+        <v>0.9008</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1695</v>
+        <v>-1.1647</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1645</v>
+        <v>-0.402</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.005</v>
+        <v>-0.7627</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2023</v>
+        <v>-0.8228</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7035</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4159</v>
+        <v>-0.1194</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9672999999999999</v>
+        <v>-0.3419</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3781</v>
+        <v>0.3014</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5891</v>
+        <v>-0.6433</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2852</v>
+        <v>-0.0163</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>-0.1209</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1322</v>
+        <v>0.1046</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>Y. MORIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3507</v>
+        <v>-1.4289</v>
       </c>
       <c r="E11" t="n">
-        <v>-19.7494</v>
+        <v>-1.9816</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3989</v>
+        <v>0.5527</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.2525</v>
+        <v>-0.7055</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8778</v>
+        <v>-0.4217</v>
       </c>
       <c r="I11" t="n">
-        <v>-15.1302</v>
+        <v>-0.2839</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.3899</v>
+        <v>-0.4958</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5379</v>
+        <v>-0.6076</v>
       </c>
       <c r="L11" t="n">
-        <v>-15.9279</v>
+        <v>0.1117</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1374999999999996</v>
+        <v>-0.2097</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6601</v>
+        <v>0.1859</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7974999999999999</v>
+        <v>-0.3956000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>5.6709</v>
+        <v>-3.8698</v>
       </c>
       <c r="Q11" t="n">
-        <v>-7.485600000000001</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>13.1562</v>
+        <v>1.8211</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3766</v>
+        <v>1.6699</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2826</v>
+        <v>1.4813</v>
       </c>
       <c r="U11" t="n">
-        <v>3.0942</v>
+        <v>0.1886</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.1457</v>
+        <v>1.4765</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.1568</v>
+        <v>2.7237</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9889</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. NIEBLA</t>
+          <t>F. MAURI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.3676</v>
+        <v>-2.2331</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3854</v>
+        <v>-1.6329</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9822</v>
+        <v>-0.6004</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.669499999999999</v>
+        <v>-2.1751</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4861</v>
+        <v>-1.1632</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1834</v>
+        <v>-1.0118</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.0708</v>
+        <v>-1.2145</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.6099</v>
+        <v>-0.7896</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4608</v>
+        <v>-0.4248999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4012</v>
+        <v>-0.9603999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1238</v>
+        <v>-0.3736</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2774000000000001</v>
+        <v>-0.5869</v>
       </c>
       <c r="P12" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4202</v>
+        <v>-0.2858000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1825</v>
+        <v>-0.4182</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2377</v>
+        <v>0.1324</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8677999999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.5068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.6799</v>
+        <v>-3.9911</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6244</v>
+        <v>-8.0305</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.055</v>
+        <v>4.0393</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6578</v>
+        <v>-4.895200000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1442</v>
+        <v>2.4866</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.8019</v>
+        <v>-7.381799999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.3298</v>
+        <v>3.6563</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8153</v>
+        <v>6.031599999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5143</v>
+        <v>-2.375600000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.987399999999999</v>
+        <v>-8.551400000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.6712</v>
+        <v>-3.545</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.3162</v>
+        <v>-5.006399999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>5.444</v>
+        <v>-2.0489</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.6198</v>
+        <v>-23.2184</v>
       </c>
       <c r="R13" t="n">
-        <v>14.0635</v>
+        <v>21.1698</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1142</v>
+        <v>4.959199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9174</v>
+        <v>3.4175</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8031000000000001</v>
+        <v>1.5418</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.351800000000001</v>
+        <v>-2.0062</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4173999999999999</v>
+        <v>8.1144</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.9345</v>
+        <v>-10.1208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.3189</v>
+        <v>-6.321600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.998800000000001</v>
+        <v>-19.9945</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.320200000000001</v>
+        <v>13.6729</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2223</v>
+        <v>-12.276</v>
       </c>
       <c r="H14" t="n">
-        <v>15.8546</v>
+        <v>2.9351</v>
       </c>
       <c r="I14" t="n">
-        <v>-19.0766</v>
+        <v>-15.2112</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9832</v>
+        <v>-12.6281</v>
       </c>
       <c r="K14" t="n">
-        <v>10.9885</v>
+        <v>3.4595</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.0052</v>
+        <v>-16.0875</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.2056</v>
+        <v>0.3519000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8659</v>
+        <v>-0.5245</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.0716</v>
+        <v>0.8763000000000003</v>
       </c>
       <c r="P14" t="n">
-        <v>3.8563</v>
+        <v>5.6909</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.6006</v>
+        <v>-7.512</v>
       </c>
       <c r="R14" t="n">
-        <v>22.4565</v>
+        <v>13.2026</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2803</v>
+        <v>4.392200000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3622</v>
+        <v>1.3064</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.08180000000000004</v>
+        <v>3.0859</v>
       </c>
       <c r="V14" t="n">
-        <v>-15.2334</v>
+        <v>-4.1286</v>
       </c>
       <c r="W14" t="n">
-        <v>9.255800000000001</v>
+        <v>-1.1609</v>
       </c>
       <c r="X14" t="n">
-        <v>-24.489</v>
+        <v>-2.9678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>D. NIEBLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-13.9396</v>
+        <v>-8.3043</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.749700000000001</v>
+        <v>-6.441</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.1898</v>
+        <v>-1.8633</v>
       </c>
       <c r="G15" t="n">
-        <v>18.642</v>
+        <v>-5.2139</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5885</v>
+        <v>-2.6998</v>
       </c>
       <c r="I15" t="n">
-        <v>17.0539</v>
+        <v>-2.5142</v>
       </c>
       <c r="J15" t="n">
-        <v>24.5394</v>
+        <v>-5.8374</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5438</v>
+        <v>-3.6175</v>
       </c>
       <c r="L15" t="n">
-        <v>18.9957</v>
+        <v>-2.2199</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.897200000000001</v>
+        <v>0.6236</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.9553</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.942</v>
+        <v>-0.2940999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.5686</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-26.5395</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>14.971</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-12.008</v>
+        <v>-3.2772</v>
       </c>
       <c r="T15" t="n">
-        <v>-8.2568</v>
+        <v>-1.4637</v>
       </c>
       <c r="U15" t="n">
-        <v>-3.7518</v>
+        <v>-1.8135</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.005000000000001</v>
+        <v>-1.6341</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>0.8603000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-11.5118</v>
+        <v>-2.4944</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.8107</v>
+        <v>-9.448600000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.7889</v>
+        <v>-4.771</v>
       </c>
       <c r="F16" t="n">
-        <v>4.978399999999999</v>
+        <v>-4.6773</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6454</v>
+        <v>-4.9797</v>
       </c>
       <c r="H16" t="n">
-        <v>18.5961</v>
+        <v>1.823400000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-21.2418</v>
+        <v>-6.803</v>
       </c>
       <c r="J16" t="n">
-        <v>6.478300000000001</v>
+        <v>6.509200000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>21.9463</v>
+        <v>4.7447</v>
       </c>
       <c r="L16" t="n">
-        <v>-15.4676</v>
+        <v>1.7642</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.123900000000001</v>
+        <v>-11.4889</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.350099999999999</v>
+        <v>-2.9212</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.773899999999999</v>
+        <v>-8.567400000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>16.1052</v>
+        <v>6.373699999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-23.3638</v>
+        <v>-8.6502</v>
       </c>
       <c r="R16" t="n">
-        <v>39.469</v>
+        <v>15.0236</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.971299999999999</v>
+        <v>-1.5102</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.974399999999999</v>
+        <v>-2.1865</v>
       </c>
       <c r="U16" t="n">
-        <v>0.002999999999999933</v>
+        <v>0.6763999999999998</v>
       </c>
       <c r="V16" t="n">
-        <v>-18.2991</v>
+        <v>-9.331899999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>7.0706</v>
+        <v>-0.4434000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-25.3699</v>
+        <v>-8.888499999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,148 +1732,304 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.5438</v>
+        <v>-11.9714</v>
       </c>
       <c r="E17" t="n">
-        <v>-17.839</v>
+        <v>-4.412099999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2951</v>
+        <v>-7.5594</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.5458</v>
+        <v>-12.5361</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.5906</v>
+        <v>14.4963</v>
       </c>
       <c r="I17" t="n">
-        <v>-10.9555</v>
+        <v>-27.0326</v>
       </c>
       <c r="J17" t="n">
-        <v>-9.006699999999999</v>
+        <v>-1.5942</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8468000000000004</v>
+        <v>11.4255</v>
       </c>
       <c r="L17" t="n">
-        <v>-8.16</v>
+        <v>-13.0199</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.539</v>
+        <v>-10.9421</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.7436</v>
+        <v>3.071</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.7954</v>
+        <v>-14.0128</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9074</v>
+        <v>7.284400000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-14.971</v>
+        <v>-22.0806</v>
       </c>
       <c r="R17" t="n">
-        <v>14.0637</v>
+        <v>29.3646</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7733</v>
+        <v>3.874900000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1253</v>
+        <v>3.0486</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6479</v>
+        <v>0.8267</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8639</v>
+        <v>-10.594</v>
       </c>
       <c r="W17" t="n">
-        <v>5.013500000000001</v>
+        <v>16.2143</v>
       </c>
       <c r="X17" t="n">
-        <v>-6.8774</v>
+        <v>-26.8081</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>A. HANGA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Joventut Badalona</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>33</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-14.6609</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-24.9034</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10.2426</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.4872000000000005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>23.4529</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-23.9404</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.942299999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26.9836</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-17.0413</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-10.4298</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-3.530799999999999</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.8991</v>
+      </c>
+      <c r="P18" t="n">
+        <v>19.8042</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-28.2265</v>
+      </c>
+      <c r="R18" t="n">
+        <v>48.0303</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-13.5556</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-13.0278</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.5275999999999998</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-20.4217</v>
+      </c>
+      <c r="W18" t="n">
+        <v>6.409099999999999</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-26.8308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>G. VIVES</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Joventut Badalona</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>29</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-15.287</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-7.9815</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-7.305299999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25.7995</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.1952</v>
+      </c>
+      <c r="I19" t="n">
+        <v>20.6045</v>
+      </c>
+      <c r="J19" t="n">
+        <v>32.8473</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8.972300000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.8753</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-7.047600000000001</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-3.7769</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-3.2706</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-12.975</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-33.6895</v>
+      </c>
+      <c r="R19" t="n">
+        <v>20.7146</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-17.0329</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-10.8805</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-6.151899999999999</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-11.0786</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.7418</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-14.8204</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Joventut Badalona</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>28</v>
-      </c>
-      <c r="D18" t="n">
-        <v>74.89659999999999</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5.042600000000007</v>
-      </c>
-      <c r="F18" t="n">
-        <v>69.8541</v>
-      </c>
-      <c r="G18" t="n">
-        <v>68.0603</v>
-      </c>
-      <c r="H18" t="n">
-        <v>94.44759999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-26.38649999999999</v>
-      </c>
-      <c r="J18" t="n">
-        <v>188.8783</v>
-      </c>
-      <c r="K18" t="n">
-        <v>141.5993</v>
-      </c>
-      <c r="L18" t="n">
-        <v>47.27979999999999</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-120.8182</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-47.1512</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-73.6674</v>
-      </c>
-      <c r="P18" t="n">
-        <v>12.4765</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-365.2027</v>
-      </c>
-      <c r="R18" t="n">
-        <v>377.6777</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5.897400000000005</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-5.197999999999993</v>
-      </c>
-      <c r="U18" t="n">
-        <v>11.0957</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-11.53780000000001</v>
-      </c>
-      <c r="W18" t="n">
-        <v>186.5624</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-198.0996</v>
+      <c r="C20" t="n">
+        <v>34</v>
+      </c>
+      <c r="D20" t="n">
+        <v>131.4793</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37.01609999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>94.46249999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>110.004</v>
+      </c>
+      <c r="H20" t="n">
+        <v>131.3473</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-21.3432</v>
+      </c>
+      <c r="J20" t="n">
+        <v>255.9426</v>
+      </c>
+      <c r="K20" t="n">
+        <v>178.6296</v>
+      </c>
+      <c r="L20" t="n">
+        <v>77.3115</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-145.9377</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-47.2816</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-98.6549</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12.5211</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-438.1926</v>
+      </c>
+      <c r="R20" t="n">
+        <v>450.7126</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.781500000000007</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-10.82569999999999</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9.046500000000002</v>
+      </c>
+      <c r="V20" t="n">
+        <v>10.7373</v>
+      </c>
+      <c r="W20" t="n">
+        <v>230.0937</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-219.357</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Joventut Badalona.xlsx
@@ -565,13 +565,13 @@
         <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>50.0479</v>
+        <v>80.0104</v>
       </c>
       <c r="E2" t="n">
-        <v>41.8679</v>
+        <v>57.0295</v>
       </c>
       <c r="F2" t="n">
-        <v>8.180099999999999</v>
+        <v>22.981</v>
       </c>
       <c r="G2" t="n">
         <v>52.7985</v>
@@ -610,13 +610,13 @@
         <v>62.1435</v>
       </c>
       <c r="S2" t="n">
-        <v>-37.4956</v>
+        <v>-7.533399999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-19.0278</v>
+        <v>-3.8666</v>
       </c>
       <c r="U2" t="n">
-        <v>-18.4676</v>
+        <v>-3.6668</v>
       </c>
       <c r="V2" t="n">
         <v>39.5252</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>37.786</v>
+        <v>36.154</v>
       </c>
       <c r="E3" t="n">
-        <v>22.3714</v>
+        <v>17.586</v>
       </c>
       <c r="F3" t="n">
-        <v>15.4144</v>
+        <v>18.568</v>
       </c>
       <c r="G3" t="n">
-        <v>8.8325</v>
+        <v>6.669300000000002</v>
       </c>
       <c r="H3" t="n">
-        <v>5.581500000000001</v>
+        <v>10.6276</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2514</v>
+        <v>-3.9582</v>
       </c>
       <c r="J3" t="n">
-        <v>21.5417</v>
+        <v>26.2416</v>
       </c>
       <c r="K3" t="n">
-        <v>10.3937</v>
+        <v>17.9314</v>
       </c>
       <c r="L3" t="n">
-        <v>11.148</v>
+        <v>8.31</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.7089</v>
+        <v>-19.5722</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.8118</v>
+        <v>-7.3037</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.896800000000001</v>
+        <v>-12.2685</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.186799999999999</v>
+        <v>-28.9092</v>
       </c>
       <c r="Q3" t="n">
-        <v>-33.2344</v>
+        <v>-82.858</v>
       </c>
       <c r="R3" t="n">
-        <v>30.0475</v>
+        <v>53.9488</v>
       </c>
       <c r="S3" t="n">
-        <v>28.5526</v>
+        <v>5.269800000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>13.778</v>
+        <v>-1.4332</v>
       </c>
       <c r="U3" t="n">
-        <v>14.7748</v>
+        <v>6.702199999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5873</v>
+        <v>53.1246</v>
       </c>
       <c r="W3" t="n">
-        <v>20.2863</v>
+        <v>75.6348</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.6988</v>
+        <v>-22.5107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>L. HAKANSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3776</v>
+        <v>35.9856</v>
       </c>
       <c r="E4" t="n">
-        <v>19.1618</v>
+        <v>12.8113</v>
       </c>
       <c r="F4" t="n">
-        <v>13.2158</v>
+        <v>23.1743</v>
       </c>
       <c r="G4" t="n">
-        <v>22.584</v>
+        <v>34.0069</v>
       </c>
       <c r="H4" t="n">
-        <v>13.5498</v>
+        <v>16.6385</v>
       </c>
       <c r="I4" t="n">
-        <v>9.0341</v>
+        <v>17.3685</v>
       </c>
       <c r="J4" t="n">
-        <v>28.201</v>
+        <v>38.9401</v>
       </c>
       <c r="K4" t="n">
-        <v>15.4661</v>
+        <v>15.9156</v>
       </c>
       <c r="L4" t="n">
-        <v>12.7349</v>
+        <v>23.024</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.6172</v>
+        <v>-4.9331</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9161</v>
+        <v>0.7227</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.7012</v>
+        <v>-5.6555</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6824999999999999</v>
+        <v>-3.641899999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-34.6</v>
+        <v>-41.4291</v>
       </c>
       <c r="R4" t="n">
-        <v>33.9174</v>
+        <v>37.7872</v>
       </c>
       <c r="S4" t="n">
-        <v>25.744</v>
+        <v>-5.417</v>
       </c>
       <c r="T4" t="n">
-        <v>20.4708</v>
+        <v>-5.8731</v>
       </c>
       <c r="U4" t="n">
-        <v>5.273400000000001</v>
+        <v>0.4559999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-15.2674</v>
+        <v>11.0377</v>
       </c>
       <c r="W4" t="n">
-        <v>5.0902</v>
+        <v>21.1734</v>
       </c>
       <c r="X4" t="n">
-        <v>-20.3579</v>
+        <v>-10.1358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>29.7093</v>
+        <v>22.6152</v>
       </c>
       <c r="E5" t="n">
-        <v>25.7585</v>
+        <v>13.0214</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9507</v>
+        <v>9.5936</v>
       </c>
       <c r="G5" t="n">
-        <v>11.0176</v>
+        <v>8.8325</v>
       </c>
       <c r="H5" t="n">
-        <v>12.7958</v>
+        <v>5.581500000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7786</v>
+        <v>3.2514</v>
       </c>
       <c r="J5" t="n">
-        <v>23.8438</v>
+        <v>21.5417</v>
       </c>
       <c r="K5" t="n">
-        <v>18.5014</v>
+        <v>10.3937</v>
       </c>
       <c r="L5" t="n">
-        <v>5.342000000000001</v>
+        <v>11.148</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.8257</v>
+        <v>-12.7089</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.7054</v>
+        <v>-4.8118</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.120200000000001</v>
+        <v>-7.896800000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>12.2919</v>
+        <v>-3.186799999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-18.2108</v>
+        <v>-33.2344</v>
       </c>
       <c r="R5" t="n">
-        <v>30.5028</v>
+        <v>30.0475</v>
       </c>
       <c r="S5" t="n">
-        <v>16.7495</v>
+        <v>13.382</v>
       </c>
       <c r="T5" t="n">
-        <v>13.0852</v>
+        <v>4.4277</v>
       </c>
       <c r="U5" t="n">
-        <v>3.6641</v>
+        <v>8.9541</v>
       </c>
       <c r="V5" t="n">
-        <v>-10.3501</v>
+        <v>3.5873</v>
       </c>
       <c r="W5" t="n">
-        <v>7.040299999999999</v>
+        <v>20.2863</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.39</v>
+        <v>-16.6988</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>24.4086</v>
+        <v>21.1912</v>
       </c>
       <c r="E6" t="n">
-        <v>7.5528</v>
+        <v>17.6346</v>
       </c>
       <c r="F6" t="n">
-        <v>16.8558</v>
+        <v>3.5562</v>
       </c>
       <c r="G6" t="n">
-        <v>6.669300000000002</v>
+        <v>11.0176</v>
       </c>
       <c r="H6" t="n">
-        <v>10.6276</v>
+        <v>12.7958</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.9582</v>
+        <v>-1.7786</v>
       </c>
       <c r="J6" t="n">
-        <v>26.2416</v>
+        <v>23.8438</v>
       </c>
       <c r="K6" t="n">
-        <v>17.9314</v>
+        <v>18.5014</v>
       </c>
       <c r="L6" t="n">
-        <v>8.31</v>
+        <v>5.342000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-19.5722</v>
+        <v>-12.8257</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.3037</v>
+        <v>-5.7054</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.2685</v>
+        <v>-7.120200000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>-28.9092</v>
+        <v>12.2919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-82.858</v>
+        <v>-18.2108</v>
       </c>
       <c r="R6" t="n">
-        <v>53.9488</v>
+        <v>30.5028</v>
       </c>
       <c r="S6" t="n">
-        <v>-6.4764</v>
+        <v>8.231300000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-11.4664</v>
+        <v>4.9617</v>
       </c>
       <c r="U6" t="n">
-        <v>4.99</v>
+        <v>3.2697</v>
       </c>
       <c r="V6" t="n">
-        <v>53.1246</v>
+        <v>-10.3501</v>
       </c>
       <c r="W6" t="n">
-        <v>75.6348</v>
+        <v>7.040299999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-22.5107</v>
+        <v>-17.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>15.7511</v>
+        <v>14.9332</v>
       </c>
       <c r="E7" t="n">
-        <v>2.531000000000001</v>
+        <v>4.5307</v>
       </c>
       <c r="F7" t="n">
-        <v>13.2196</v>
+        <v>10.4023</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.782</v>
+        <v>22.584</v>
       </c>
       <c r="H7" t="n">
-        <v>9.505599999999999</v>
+        <v>13.5498</v>
       </c>
       <c r="I7" t="n">
-        <v>-17.2872</v>
+        <v>9.0341</v>
       </c>
       <c r="J7" t="n">
-        <v>12.3549</v>
+        <v>28.201</v>
       </c>
       <c r="K7" t="n">
-        <v>17.8345</v>
+        <v>15.4661</v>
       </c>
       <c r="L7" t="n">
-        <v>-5.4795</v>
+        <v>12.7349</v>
       </c>
       <c r="M7" t="n">
-        <v>-20.1368</v>
+        <v>-5.6172</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.3291</v>
+        <v>-1.9161</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.8077</v>
+        <v>-3.7012</v>
       </c>
       <c r="P7" t="n">
-        <v>18.8938</v>
+        <v>-0.6824999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-30.7306</v>
+        <v>-34.6</v>
       </c>
       <c r="R7" t="n">
-        <v>49.6243</v>
+        <v>33.9174</v>
       </c>
       <c r="S7" t="n">
-        <v>18.9297</v>
+        <v>8.299900000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>11.0002</v>
+        <v>5.8393</v>
       </c>
       <c r="U7" t="n">
-        <v>7.930000000000001</v>
+        <v>2.4601</v>
       </c>
       <c r="V7" t="n">
-        <v>-14.2909</v>
+        <v>-15.2674</v>
       </c>
       <c r="W7" t="n">
-        <v>9.9064</v>
+        <v>5.0902</v>
       </c>
       <c r="X7" t="n">
-        <v>-24.1972</v>
+        <v>-20.3579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. HAKANSON</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>14.4056</v>
+        <v>5.7987</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.068400000000001</v>
+        <v>-3.7949</v>
       </c>
       <c r="F8" t="n">
-        <v>15.4738</v>
+        <v>9.593299999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>34.0069</v>
+        <v>-7.782</v>
       </c>
       <c r="H8" t="n">
-        <v>16.6385</v>
+        <v>9.505599999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>17.3685</v>
+        <v>-17.2872</v>
       </c>
       <c r="J8" t="n">
-        <v>38.9401</v>
+        <v>12.3549</v>
       </c>
       <c r="K8" t="n">
-        <v>15.9156</v>
+        <v>17.8345</v>
       </c>
       <c r="L8" t="n">
-        <v>23.024</v>
+        <v>-5.4795</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.9331</v>
+        <v>-20.1368</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7227</v>
+        <v>-8.3291</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.6555</v>
+        <v>-11.8077</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.641899999999999</v>
+        <v>18.8938</v>
       </c>
       <c r="Q8" t="n">
-        <v>-41.4291</v>
+        <v>-30.7306</v>
       </c>
       <c r="R8" t="n">
-        <v>37.7872</v>
+        <v>49.6243</v>
       </c>
       <c r="S8" t="n">
-        <v>-26.9965</v>
+        <v>8.977399999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-19.7522</v>
+        <v>4.6741</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.2443</v>
+        <v>4.3036</v>
       </c>
       <c r="V8" t="n">
-        <v>11.0377</v>
+        <v>-14.2909</v>
       </c>
       <c r="W8" t="n">
-        <v>21.1734</v>
+        <v>9.9064</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.1358</v>
+        <v>-24.1972</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.7772</v>
       </c>
       <c r="E9" t="n">
         <v>-0.06670000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7497</v>
+        <v>0.8438</v>
       </c>
       <c r="G9" t="n">
         <v>0.5111</v>
@@ -1156,13 +1156,13 @@
         <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.007000000000000003</v>
+        <v>0.0872</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06269999999999999</v>
+        <v>0.1569</v>
       </c>
       <c r="V9" t="n">
         <v>1.0895</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0429</v>
+        <v>0.4693</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9437</v>
+        <v>-0.5884</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9008</v>
+        <v>1.0576</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1647</v>
@@ -1234,13 +1234,13 @@
         <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0163</v>
+        <v>0.4958</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1209</v>
+        <v>0.2345</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1046</v>
+        <v>0.2614</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. MORIN</t>
+          <t>F. MAURI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4289</v>
+        <v>-2.1391</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9816</v>
+        <v>-1.6329</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5527</v>
+        <v>-0.5063</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7055</v>
+        <v>-2.1751</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4217</v>
+        <v>-1.1632</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2839</v>
+        <v>-1.0118</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4958</v>
+        <v>-1.2145</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6076</v>
+        <v>-0.7896</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1117</v>
+        <v>-0.4248999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2097</v>
+        <v>-0.9603999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1859</v>
+        <v>-0.3736</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3956000000000001</v>
+        <v>-0.5869</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8698</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.690799999999999</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8211</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6699</v>
+        <v>-0.1917</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4813</v>
+        <v>-0.4182</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1886</v>
+        <v>0.2266</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4765</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7237</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2472</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. MAURI</t>
+          <t>Y. MORIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2331</v>
+        <v>-2.8188</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6329</v>
+        <v>-3.403</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6004</v>
+        <v>0.5840999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1751</v>
+        <v>-0.7055</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1632</v>
+        <v>-0.4217</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0118</v>
+        <v>-0.2839</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2145</v>
+        <v>-0.4958</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7896</v>
+        <v>-0.6076</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4248999999999999</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9603999999999999</v>
+        <v>-0.2097</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3736</v>
+        <v>0.1859</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5869</v>
+        <v>-0.3956000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2276</v>
+        <v>-3.8698</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2276</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2858000000000001</v>
+        <v>0.2798999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4182</v>
+        <v>0.05990000000000004</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1324</v>
+        <v>0.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4765</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9911</v>
+        <v>-2.928599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.0305</v>
+        <v>-16.3952</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0393</v>
+        <v>13.4669</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.895200000000001</v>
+        <v>-0.4872000000000005</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4866</v>
+        <v>23.4529</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.381799999999999</v>
+        <v>-23.9404</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6563</v>
+        <v>9.942299999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.031599999999999</v>
+        <v>26.9836</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.375600000000001</v>
+        <v>-17.0413</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.551400000000001</v>
+        <v>-10.4298</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.545</v>
+        <v>-3.530799999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.006399999999999</v>
+        <v>-6.8991</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0489</v>
+        <v>19.8042</v>
       </c>
       <c r="Q13" t="n">
-        <v>-23.2184</v>
+        <v>-28.2265</v>
       </c>
       <c r="R13" t="n">
-        <v>21.1698</v>
+        <v>48.0303</v>
       </c>
       <c r="S13" t="n">
-        <v>4.959199999999999</v>
+        <v>-1.8229</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4175</v>
+        <v>-4.5203</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5418</v>
+        <v>2.6973</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.0062</v>
+        <v>-20.4217</v>
       </c>
       <c r="W13" t="n">
-        <v>8.1144</v>
+        <v>6.409099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.1208</v>
+        <v>-26.8308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. DEKKER</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.321600000000001</v>
+        <v>-3.346100000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.9945</v>
+        <v>-1.410900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>13.6729</v>
+        <v>-1.9353</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.276</v>
+        <v>25.7995</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9351</v>
+        <v>5.1952</v>
       </c>
       <c r="I14" t="n">
-        <v>-15.2112</v>
+        <v>20.6045</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.6281</v>
+        <v>32.8473</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4595</v>
+        <v>8.972300000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-16.0875</v>
+        <v>23.8753</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3519000000000001</v>
+        <v>-7.047600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5245</v>
+        <v>-3.7769</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8763000000000003</v>
+        <v>-3.2706</v>
       </c>
       <c r="P14" t="n">
-        <v>5.6909</v>
+        <v>-12.975</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.512</v>
+        <v>-33.6895</v>
       </c>
       <c r="R14" t="n">
-        <v>13.2026</v>
+        <v>20.7146</v>
       </c>
       <c r="S14" t="n">
-        <v>4.392200000000001</v>
+        <v>-5.0921</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3064</v>
+        <v>-4.3102</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0859</v>
+        <v>-0.7811999999999997</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.1286</v>
+        <v>-11.0786</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.1609</v>
+        <v>3.7418</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.9678</v>
+        <v>-14.8204</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. NIEBLA</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.3043</v>
+        <v>-5.0001</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.441</v>
+        <v>-9.3888</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8633</v>
+        <v>4.3889</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.2139</v>
+        <v>-4.895200000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.6998</v>
+        <v>2.4866</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.5142</v>
+        <v>-7.381799999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.8374</v>
+        <v>3.6563</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.6175</v>
+        <v>6.031599999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.2199</v>
+        <v>-2.375600000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6236</v>
+        <v>-8.551400000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9177999999999999</v>
+        <v>-3.545</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2940999999999999</v>
+        <v>-5.006399999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8211</v>
+        <v>-2.0489</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-23.2184</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8211</v>
+        <v>21.1698</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.2772</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4637</v>
+        <v>2.0588</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.8135</v>
+        <v>1.8912</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.6341</v>
+        <v>-2.0062</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8603000000000001</v>
+        <v>8.1144</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4944</v>
+        <v>-10.1208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>D. NIEBLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-9.448600000000001</v>
+        <v>-6.2544</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.771</v>
+        <v>-5.0195</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.6773</v>
+        <v>-1.2349</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.9797</v>
+        <v>-5.2139</v>
       </c>
       <c r="H16" t="n">
-        <v>1.823400000000001</v>
+        <v>-2.6998</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.803</v>
+        <v>-2.5142</v>
       </c>
       <c r="J16" t="n">
-        <v>6.509200000000001</v>
+        <v>-5.8374</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7447</v>
+        <v>-3.6175</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7642</v>
+        <v>-2.2199</v>
       </c>
       <c r="M16" t="n">
-        <v>-11.4889</v>
+        <v>0.6236</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.9212</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.567400000000001</v>
+        <v>-0.2940999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>6.373699999999999</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-8.6502</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>15.0236</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5102</v>
+        <v>-1.2274</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.1865</v>
+        <v>-0.04239999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6763999999999998</v>
+        <v>-1.1852</v>
       </c>
       <c r="V16" t="n">
-        <v>-9.331899999999999</v>
+        <v>-1.6341</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.4434000000000001</v>
+        <v>0.8603000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.888499999999999</v>
+        <v>-2.4944</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>S. DEKKER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.9714</v>
+        <v>-7.9253</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.412099999999999</v>
+        <v>-21.5689</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.5594</v>
+        <v>13.6436</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.5361</v>
+        <v>-12.276</v>
       </c>
       <c r="H17" t="n">
-        <v>14.4963</v>
+        <v>2.9351</v>
       </c>
       <c r="I17" t="n">
-        <v>-27.0326</v>
+        <v>-15.2112</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5942</v>
+        <v>-12.6281</v>
       </c>
       <c r="K17" t="n">
-        <v>11.4255</v>
+        <v>3.4595</v>
       </c>
       <c r="L17" t="n">
-        <v>-13.0199</v>
+        <v>-16.0875</v>
       </c>
       <c r="M17" t="n">
-        <v>-10.9421</v>
+        <v>0.3519000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>3.071</v>
+        <v>-0.5245</v>
       </c>
       <c r="O17" t="n">
-        <v>-14.0128</v>
+        <v>0.8763000000000003</v>
       </c>
       <c r="P17" t="n">
-        <v>7.284400000000001</v>
+        <v>5.6909</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.0806</v>
+        <v>-7.512</v>
       </c>
       <c r="R17" t="n">
-        <v>29.3646</v>
+        <v>13.2026</v>
       </c>
       <c r="S17" t="n">
-        <v>3.874900000000001</v>
+        <v>2.7888</v>
       </c>
       <c r="T17" t="n">
-        <v>3.0486</v>
+        <v>-0.2680000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8267</v>
+        <v>3.0569</v>
       </c>
       <c r="V17" t="n">
-        <v>-10.594</v>
+        <v>-4.1286</v>
       </c>
       <c r="W17" t="n">
-        <v>16.2143</v>
+        <v>-1.1609</v>
       </c>
       <c r="X17" t="n">
-        <v>-26.8081</v>
+        <v>-2.9678</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-14.6609</v>
+        <v>-8.9535</v>
       </c>
       <c r="E18" t="n">
-        <v>-24.9034</v>
+        <v>-4.938199999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>10.2426</v>
+        <v>-4.0152</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4872000000000005</v>
+        <v>-4.9797</v>
       </c>
       <c r="H18" t="n">
-        <v>23.4529</v>
+        <v>1.823400000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-23.9404</v>
+        <v>-6.803</v>
       </c>
       <c r="J18" t="n">
-        <v>9.942299999999999</v>
+        <v>6.509200000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>26.9836</v>
+        <v>4.7447</v>
       </c>
       <c r="L18" t="n">
-        <v>-17.0413</v>
+        <v>1.7642</v>
       </c>
       <c r="M18" t="n">
-        <v>-10.4298</v>
+        <v>-11.4889</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.530799999999999</v>
+        <v>-2.9212</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.8991</v>
+        <v>-8.567400000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>19.8042</v>
+        <v>6.373699999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-28.2265</v>
+        <v>-8.6502</v>
       </c>
       <c r="R18" t="n">
-        <v>48.0303</v>
+        <v>15.0236</v>
       </c>
       <c r="S18" t="n">
-        <v>-13.5556</v>
+        <v>-1.0156</v>
       </c>
       <c r="T18" t="n">
-        <v>-13.0278</v>
+        <v>-2.3539</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5275999999999998</v>
+        <v>1.3381</v>
       </c>
       <c r="V18" t="n">
-        <v>-20.4217</v>
+        <v>-9.331899999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>6.409099999999999</v>
+        <v>-0.4434000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-26.8308</v>
+        <v>-8.888499999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-15.287</v>
+        <v>-12.9442</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.9815</v>
+        <v>-6.9341</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.305299999999999</v>
+        <v>-6.009899999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>25.7995</v>
+        <v>-12.5361</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1952</v>
+        <v>14.4963</v>
       </c>
       <c r="I19" t="n">
-        <v>20.6045</v>
+        <v>-27.0326</v>
       </c>
       <c r="J19" t="n">
-        <v>32.8473</v>
+        <v>-1.5942</v>
       </c>
       <c r="K19" t="n">
-        <v>8.972300000000001</v>
+        <v>11.4255</v>
       </c>
       <c r="L19" t="n">
-        <v>23.8753</v>
+        <v>-13.0199</v>
       </c>
       <c r="M19" t="n">
-        <v>-7.047600000000001</v>
+        <v>-10.9421</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.7769</v>
+        <v>3.071</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.2706</v>
+        <v>-14.0128</v>
       </c>
       <c r="P19" t="n">
-        <v>-12.975</v>
+        <v>7.284400000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>-33.6895</v>
+        <v>-22.0806</v>
       </c>
       <c r="R19" t="n">
-        <v>20.7146</v>
+        <v>29.3646</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.0329</v>
+        <v>2.9017</v>
       </c>
       <c r="T19" t="n">
-        <v>-10.8805</v>
+        <v>0.5266000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.151899999999999</v>
+        <v>2.3753</v>
       </c>
       <c r="V19" t="n">
-        <v>-11.0786</v>
+        <v>-10.594</v>
       </c>
       <c r="W19" t="n">
-        <v>3.7418</v>
+        <v>16.2143</v>
       </c>
       <c r="X19" t="n">
-        <v>-14.8204</v>
+        <v>-26.8081</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>34</v>
       </c>
       <c r="D20" t="n">
-        <v>131.4793</v>
+        <v>165.6247</v>
       </c>
       <c r="E20" t="n">
-        <v>37.01609999999999</v>
+        <v>47.472</v>
       </c>
       <c r="F20" t="n">
-        <v>94.46249999999999</v>
+        <v>118.152</v>
       </c>
       <c r="G20" t="n">
         <v>110.004</v>
@@ -2002,7 +2002,7 @@
         <v>-47.2816</v>
       </c>
       <c r="O20" t="n">
-        <v>-98.6549</v>
+        <v>-98.65490000000001</v>
       </c>
       <c r="P20" t="n">
         <v>12.5211</v>
@@ -2014,13 +2014,13 @@
         <v>450.7126</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.781500000000007</v>
+        <v>32.3637</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.82569999999999</v>
+        <v>-0.3729999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>9.046500000000002</v>
+        <v>32.7362</v>
       </c>
       <c r="V20" t="n">
         <v>10.7373</v>
